--- a/pacjenci/EWELINA STRZYŻ.xlsx
+++ b/pacjenci/EWELINA STRZYŻ.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,10 +527,14 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -574,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/EWELINA STRZYŻ.xlsx
+++ b/pacjenci/EWELINA STRZYŻ.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>08.11.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T. Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 85 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Bardzo liczne, pojedyncze i spakietowane, aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 27x21 mm SUV max do 5,9 - po stronie lewej wielkości do 38x20 mm SUV max do 5,4 Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.  Klatka piersiowa i śródpiersie: Liczne, aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane : - międzypiersiowe i pachowe prawe wielkości do 27x22 mm SUV max do 5,8 - międzypiersiowe i pachowe lewe wielkości do 24x25 mm SUV max do 6,3 - przytchawicze górne i dolne prawe wielkości do 10 mm SUV max do 3,6 - lewobocznie od łuku aorty oraz przymostkowe prawe i lewe wielkości do 10 mm wg PET SUV max do 4,3 - podostrogowe wielkości do 29x16 mm wg PET SUV max do 4,3 - wnęki płuca prawego SUV max do 3,5 - wnęki płuca lewego SUV max do 3,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc. Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane: - we wnęce śledziony średnicy do 12 mm wg PET SUV max do 5,1 - we wnęce wątroby wielkości do 20 mm wg PET SUV max 4,5 [Im fuz. 169] - drobne, pojedyncze okołoaortalne obustronnie średnicy do 11 mm wg PET SUV max do 4,1 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x30 mm SUV max do 5,6 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 16x23 mm SUV max do 5,68 - pachwinowe i udowe prawe wielkości do 20x11 mm SUV max do 5,2 - pachwinowe i udowe lewe wielkości do 23x15 mm SUV max do 5,5  Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości 127x59x168 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 471] Drobny konkrement w nerce prawej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, zwłaszcza w zakresie kości ramiennych i udowych obustronnie.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,4 Prawy płat wątroby SUVmax do 2,5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony oraz  bardzo licznych grup węzłów chłonnych po  obu stronach przepony. Niewykluczone zajęcie szpiku kostnego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6.3</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>14.02.2023</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T. Ocena odpowiedzi po 3 cyklach leczenia.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 82mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 18x10 mm SUV max do 4,3, - po stronie lewej wielkości do 17x10 mm SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.  Klatka piersiowa i śródpiersie: Aktywne  i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 16 mm SUV max do 4,1, - międzypiersiowe i pachowe lewe wielkości do 15 mm SUV max do 3,5, - przytchawicze  prawe wielkości do 9 mm SUV max do 2,9, - podostrogowe wielkości do 19x10 mm wg PET SUV max do 3,8, - wnęki płuca prawego SUV max do 3,9, - wnęki płuca lewego SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc.  Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - we wnęce wątroby wielkości do 9 mm wg PET SUV max 3,3 [Im fuz. 166], - pachwinowe i udowe prawe wielkości do 10 mm SUV max do 3,0, - pachwinowe i udowe lewe wielkości do 15 mm SUV max do 3,2. Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości do 122mm SUV max do 3,0. Rozlanie zwiększony metabolizm FDG w okrężnicy, SUV max do 9,5 - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 459] Drobny konkrement w nerce prawej.  Układ kostny: Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max 4,7.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego z zajęciem chłonnych po obu stronach przepony. W porównaniu badania wyjściowego z 08.11.2022 częściowa regresja radiologiczna i metaboliczna zmian.  Niewykluczone zajęcie szpiku kostnego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>9.5</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>16.05.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Obwodowy chłoniak z komórek T. Ocena odpowiedzi po 6 cyklu leczenia.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 82 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w głowy i szyi. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy prawej zatoki czołowej. Niewielkie przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej. Węzły chłonne szyjne wielkości do 14x9 mm [największy grupy 1B po stronie lewej].  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - pachowe prawe wielkości do 9x16 mm SUV max do 2,2; - pachowe lewe wielkości do 15x8 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Drobne zmiany włókniste w szczytach obu płuc. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Pęcherz rozedmowy w grzbietowej części segm. 10 płuca lewego, wielkości 12x21mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Niejednorodny metabolizm FDG w  śledzionie. Rozlanie wzmożony metabolizm FDG w żołądku SUV max 4,1- odczynowo? Odcinkowo zwiększony metabolizm FDG w  jelitach  SUV max do 3,5- w pierwszej kolejności o charakterze czynnościowym. Wzmożony metabolizm FDG w guzku nadnercza lewego, wielkości 20x15mm, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 5mm zwapnienie w segmencie 4b wątroby [Im CT 465]. Drobny uwapniony konkrement w UKM-ie nerki prawej. Uchyłki esicy.  Układ kostny: Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max do 3,6.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w lewym stawie krzyżowo-biodrowym.  Inne: Wzmożony metabolizm FDG w mięśniach grzbietu   Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG uwidoczniono obecność jedynie pobudzonych metabolicznie węzłów chłonnych pachowych- dobra odpowiedź metaboliczna choroby na stosowane leczenie z częściową regresją radiologiczną zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/EWELINA STRZYŻ.xlsx
+++ b/pacjenci/EWELINA STRZYŻ.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 85 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Bardzo liczne, pojedyncze i spakietowane, aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 27x21 mm SUV max do 5,9 - po stronie lewej wielkości do 38x20 mm SUV max do 5,4 Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.  Klatka piersiowa i śródpiersie: Liczne, aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane : - międzypiersiowe i pachowe prawe wielkości do 27x22 mm SUV max do 5,8 - międzypiersiowe i pachowe lewe wielkości do 24x25 mm SUV max do 6,3 - przytchawicze górne i dolne prawe wielkości do 10 mm SUV max do 3,6 - lewobocznie od łuku aorty oraz przymostkowe prawe i lewe wielkości do 10 mm wg PET SUV max do 4,3 - podostrogowe wielkości do 29x16 mm wg PET SUV max do 4,3 - wnęki płuca prawego SUV max do 3,5 - wnęki płuca lewego SUV max do 3,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc. Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane: - we wnęce śledziony średnicy do 12 mm wg PET SUV max do 5,1 - we wnęce wątroby wielkości do 20 mm wg PET SUV max 4,5 [Im fuz. 169] - drobne, pojedyncze okołoaortalne obustronnie średnicy do 11 mm wg PET SUV max do 4,1 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x30 mm SUV max do 5,6 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 16x23 mm SUV max do 5,68 - pachwinowe i udowe prawe wielkości do 20x11 mm SUV max do 5,2 - pachwinowe i udowe lewe wielkości do 23x15 mm SUV max do 5,5  Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości 127x59x168 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 471] Drobny konkrement w nerce prawej.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, zwłaszcza w zakresie kości ramiennych i udowych obustronnie.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,4 Prawy płat wątroby SUVmax do 2,5</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Bardzo liczne, pojedyncze i spakietowane, aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 27x21 mm SUV max do 5,9 - po stronie lewej wielkości do 38x20 mm SUV max do 5,4 Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Liczne, aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane : - międzypiersiowe i pachowe prawe wielkości do 27x22 mm SUV max do 5,8 - międzypiersiowe i pachowe lewe wielkości do 24x25 mm SUV max do 6,3 - przytchawicze górne i dolne prawe wielkości do 10 mm SUV max do 3,6 - lewobocznie od łuku aorty oraz przymostkowe prawe i lewe wielkości do 10 mm wg PET SUV max do 4,3 - podostrogowe wielkości do 29x16 mm wg PET SUV max do 4,3 - wnęki płuca prawego SUV max do 3,5 - wnęki płuca lewego SUV max do 3,3 Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc. Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne, pojedyncze i spakietowane: - we wnęce śledziony średnicy do 12 mm wg PET SUV max do 5,1 - we wnęce wątroby wielkości do 20 mm wg PET SUV max 4,5 [Im fuz. 169] - drobne, pojedyncze okołoaortalne obustronnie średnicy do 11 mm wg PET SUV max do 4,1 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych wielkości do 19x30 mm SUV max do 5,6 - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych wielkości do 16x23 mm SUV max do 5,68 - pachwinowe i udowe prawe wielkości do 20x11 mm SUV max do 5,2 - pachwinowe i udowe lewe wielkości do 23x15 mm SUV max do 5,5  Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości 127x59x168 mm SUV max do 5,0 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 471] Drobny konkrement w nerce prawej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, zwłaszcza w zakresie kości ramiennych i udowych obustronnie.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony oraz  bardzo licznych grup węzłów chłonnych po  obu stronach przepony. Niewykluczone zajęcie szpiku kostnego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>6.3</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 82mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 18x10 mm SUV max do 4,3, - po stronie lewej wielkości do 17x10 mm SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.  Klatka piersiowa i śródpiersie: Aktywne  i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 16 mm SUV max do 4,1, - międzypiersiowe i pachowe lewe wielkości do 15 mm SUV max do 3,5, - przytchawicze  prawe wielkości do 9 mm SUV max do 2,9, - podostrogowe wielkości do 19x10 mm wg PET SUV max do 3,8, - wnęki płuca prawego SUV max do 3,9, - wnęki płuca lewego SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc.  Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne: - we wnęce wątroby wielkości do 9 mm wg PET SUV max 3,3 [Im fuz. 166], - pachwinowe i udowe prawe wielkości do 10 mm SUV max do 3,0, - pachwinowe i udowe lewe wielkości do 15 mm SUV max do 3,2. Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości do 122mm SUV max do 3,0. Rozlanie zwiększony metabolizm FDG w okrężnicy, SUV max do 9,5 - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 459] Drobny konkrement w nerce prawej.  Układ kostny: Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max 4,7.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne szyjne,wszystkich grup, obustronnie: - po stronie prawej wielkości do 18x10 mm SUV max do 4,3, - po stronie lewej wielkości do 17x10 mm SUV max do 4,3. Poza tym fizjologiczny metabolizm FDG w głowy i szyi. W lewej zatoce szczękowej pogrubienie błony śluzowej przy ścianie górnej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywne  i pobudzone metabolicznie węzły chłonne: - międzypiersiowe i pachowe prawe wielkości do 16 mm SUV max do 4,1, - międzypiersiowe i pachowe lewe wielkości do 15 mm SUV max do 3,5, - przytchawicze  prawe wielkości do 9 mm SUV max do 2,9, - podostrogowe wielkości do 19x10 mm wg PET SUV max do 3,8, - wnęki płuca prawego SUV max do 3,9, - wnęki płuca lewego SUV max do 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Niewielkie zmiany bliznowate w grzbietowych partiach płatów dolnych obustronnie oraz w przypodstawnych partiach płuc.  Pęcherz rozedmowy w grzbietowej części s. 10 PL wlk. 12x21mm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne: - we wnęce wątroby wielkości do 9 mm wg PET SUV max 3,3 [Im fuz. 166], - pachwinowe i udowe prawe wielkości do 10 mm SUV max do 3,0, - pachwinowe i udowe lewe wielkości do 15 mm SUV max do 3,2. Rozlanie wzmożony metabolizm FDG w znacznie powiększonej śledzionie wielkości do 122mm SUV max do 3,0. Rozlanie zwiększony metabolizm FDG w okrężnicy, SUV max do 9,5 - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Drobne zwapnienie w segmencie 4b wątroby [Im CT 459] Drobny konkrement w nerce prawej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max 4,7.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym oraz  na poziomie L5/S1.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego z zajęciem chłonnych po obu stronach przepony. W porównaniu badania wyjściowego z 08.11.2022 częściowa regresja radiologiczna i metaboliczna zmian.  Niewykluczone zajęcie szpiku kostnego. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 82 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w głowy i szyi. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy prawej zatoki czołowej. Niewielkie przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej. Węzły chłonne szyjne wielkości do 14x9 mm [największy grupy 1B po stronie lewej].  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - pachowe prawe wielkości do 9x16 mm SUV max do 2,2; - pachowe lewe wielkości do 15x8 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Drobne zmiany włókniste w szczytach obu płuc. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Pęcherz rozedmowy w grzbietowej części segm. 10 płuca lewego, wielkości 12x21mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Niejednorodny metabolizm FDG w  śledzionie. Rozlanie wzmożony metabolizm FDG w żołądku SUV max 4,1- odczynowo? Odcinkowo zwiększony metabolizm FDG w  jelitach  SUV max do 3,5- w pierwszej kolejności o charakterze czynnościowym. Wzmożony metabolizm FDG w guzku nadnercza lewego, wielkości 20x15mm, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 5mm zwapnienie w segmencie 4b wątroby [Im CT 465]. Drobny uwapniony konkrement w UKM-ie nerki prawej. Uchyłki esicy.  Układ kostny: Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max do 3,6.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w lewym stawie krzyżowo-biodrowym.  Inne: Wzmożony metabolizm FDG w mięśniach grzbietu   Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w głowy i szyi. Niewielkie zgrubienia błony śluzowej w sitowiu obustronnie oraz u podstawy prawej zatoki czołowej. Niewielkie przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej. Węzły chłonne szyjne wielkości do 14x9 mm [największy grupy 1B po stronie lewej].</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: - pachowe prawe wielkości do 9x16 mm SUV max do 2,2; - pachowe lewe wielkości do 15x8 mm SUV max do 1,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne węzły chłonne położone lewobocznie od łuku aorty. Drobne zmiany włókniste w szczytach obu płuc. Drobne obwodowe pęcherze rozedmowe w płatach dolnych obu płuc. Pęcherz rozedmowy w grzbietowej części segm. 10 płuca lewego, wielkości 12x21mm. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w  śledzionie. Rozlanie wzmożony metabolizm FDG w żołądku SUV max 4,1- odczynowo? Odcinkowo zwiększony metabolizm FDG w  jelitach  SUV max do 3,5- w pierwszej kolejności o charakterze czynnościowym. Wzmożony metabolizm FDG w guzku nadnercza lewego, wielkości 20x15mm, SUV max 2,8. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 5mm zwapnienie w segmencie 4b wątroby [Im CT 465]. Drobny uwapniony konkrement w UKM-ie nerki prawej. Uchyłki esicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Rozlany, niejednorodny metabolizm FDG w układzie kostnym objętym badaniem, SUV max do 3,6.  Zmiany zwyrodnieniowe kręgosłupa. Wielopoziomowo dyskopatie w odcinku szyjnym i piersiowym kręgosłupa. Zmiany zwyrodnieniowo-wytwórcze w lewym stawie krzyżowo-biodrowym.  Inne: Wzmożony metabolizm FDG w mięśniach grzbietu</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG uwidoczniono obecność jedynie pobudzonych metabolicznie węzłów chłonnych pachowych- dobra odpowiedź metaboliczna choroby na stosowane leczenie z częściową regresją radiologiczną zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.1</v>
       </c>
     </row>
